--- a/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
+++ b/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
@@ -16,11 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,39 +27,25 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,42 +53,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,16 +429,6 @@
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -541,210 +487,201 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>0.0114</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>0.0106</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" t="n">
         <v>1.08</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" t="n">
         <v>57</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>5000</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="7" t="n">
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>32</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" t="n">
         <v>0.008800000000000001</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" t="n">
         <v>0.008</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" t="n">
         <v>44</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="7" t="n">
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>64</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>0.003</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>0.0056</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" t="n">
         <v>0.54</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>5000</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="7" t="n">
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>128</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" t="n">
         <v>0.0012</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" t="n">
         <v>0.002</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" t="n">
         <v>0.6</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>5000</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="7" t="n">
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>256</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" t="n">
         <v>0.00015</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>20000</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="7" t="n">
+      <c r="G9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>512</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="C10" s="5" t="n">
+      <c r="B10" t="n">
         <v>0.0004</v>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="7" t="n">
+      <c r="C10" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>1024</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>0.000385</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.000485</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>33725</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="7" t="n">
+      <c r="B11" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="7" t="n">
+      <c r="G13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
+++ b/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
@@ -595,19 +595,19 @@
         <v>256</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00015</v>
+        <v>4e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="G9" t="n">
         <v>0.5</v>

--- a/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
+++ b/results/bemac/bemac_classB_Ru50_Rv70_nn_vs_sc/nn_vs_sc_classB_Ru50_Rv70.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,7 +440,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Capacity: I(Z;X)=0.5000 | I(Z;Y|X)=1.0000 | I(Z;X,Y)=1.5000 | Path: U^(N/2) V^N U^(N/2)</t>
+          <t>Capacity: I(Z;X)=0.5000 | I(Z;Y|X)=1.0000 | Frozen sets: 50K MC trials</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
         <v>512</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G10" t="n">
         <v>0.5</v>
@@ -647,38 +647,25 @@
         <v>1024</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
